--- a/artfynd/A 21979-2026 artfynd.xlsx
+++ b/artfynd/A 21979-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -995,6 +995,1787 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>133730284</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79334</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Västra Hundberget, Västra Hundberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>637114</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7033908</v>
+      </c>
+      <c r="S5" t="n">
+        <v>15</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>133733485</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58119</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Tjärdalsmyran, Tjärdalsmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>637340</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7033940</v>
+      </c>
+      <c r="S6" t="n">
+        <v>15</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>133734508</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79334</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Tjärdalsmyran, Tjärdalsmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>637409</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7033890</v>
+      </c>
+      <c r="S7" t="n">
+        <v>15</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>133727592</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57955</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Tjärdalsmyran, Tjärdalsmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>637342</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7033896</v>
+      </c>
+      <c r="S8" t="n">
+        <v>15</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>133733700</v>
+      </c>
+      <c r="B9" t="n">
+        <v>91885</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Tjärdalsmyran, Tjärdalsmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>637352</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7033886</v>
+      </c>
+      <c r="S9" t="n">
+        <v>15</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>133734358</v>
+      </c>
+      <c r="B10" t="n">
+        <v>97999</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Tjärdalsmyran, Tjärdalsmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>637412</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7033897</v>
+      </c>
+      <c r="S10" t="n">
+        <v>15</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>133727622</v>
+      </c>
+      <c r="B11" t="n">
+        <v>58444</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>103018</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Svartvit flugsnappare</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Ficedula hypoleuca</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Tjärdalsmyran, Tjärdalsmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>637334</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7033909</v>
+      </c>
+      <c r="S11" t="n">
+        <v>15</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>133729318</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79334</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Tjärdalsmyran, Tjärdalsmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>637252</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7033874</v>
+      </c>
+      <c r="S12" t="n">
+        <v>15</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>133733946</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79334</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Tjärdalsmyran, Tjärdalsmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>637400</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7033911</v>
+      </c>
+      <c r="S13" t="n">
+        <v>15</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>133734071</v>
+      </c>
+      <c r="B14" t="n">
+        <v>79334</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Tjärdalsmyran, Tjärdalsmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>637391</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7033944</v>
+      </c>
+      <c r="S14" t="n">
+        <v>15</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>133729658</v>
+      </c>
+      <c r="B15" t="n">
+        <v>79334</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Västra Hundberget, Västra Hundberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>637114</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7033888</v>
+      </c>
+      <c r="S15" t="n">
+        <v>15</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>133734499</v>
+      </c>
+      <c r="B16" t="n">
+        <v>91885</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Tjärdalsmyran, Tjärdalsmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>637409</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7033890</v>
+      </c>
+      <c r="S16" t="n">
+        <v>15</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>133735008</v>
+      </c>
+      <c r="B17" t="n">
+        <v>91922</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Tjärdalsmyran, Tjärdalsmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>637370</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7033895</v>
+      </c>
+      <c r="S17" t="n">
+        <v>15</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>133728537</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79334</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Tjärdalsmyran, Tjärdalsmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>637300</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7033916</v>
+      </c>
+      <c r="S18" t="n">
+        <v>15</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>133730321</v>
+      </c>
+      <c r="B19" t="n">
+        <v>91922</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Västra Hundberget, Västra Hundberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>637161</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7033917</v>
+      </c>
+      <c r="S19" t="n">
+        <v>15</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>133730258</v>
+      </c>
+      <c r="B20" t="n">
+        <v>91885</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Västra Hundberget, Västra Hundberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>637117</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7033918</v>
+      </c>
+      <c r="S20" t="n">
+        <v>15</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>133727574</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57958</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Tjärdalsmyran, Tjärdalsmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>637328</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7033886</v>
+      </c>
+      <c r="S21" t="n">
+        <v>15</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>133734225</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57958</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Tjärdalsmyran, Tjärdalsmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>637416</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7033933</v>
+      </c>
+      <c r="S22" t="n">
+        <v>15</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gran</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 21979-2026 artfynd.xlsx
+++ b/artfynd/A 21979-2026 artfynd.xlsx
@@ -1095,10 +1095,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133733485</v>
+        <v>133727592</v>
       </c>
       <c r="B6" t="n">
-        <v>58119</v>
+        <v>57955</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1106,27 +1106,27 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1135,10 +1135,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>637340</v>
+        <v>637342</v>
       </c>
       <c r="R6" t="n">
-        <v>7033940</v>
+        <v>7033896</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1294,10 +1294,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133727592</v>
+        <v>133733485</v>
       </c>
       <c r="B8" t="n">
-        <v>57955</v>
+        <v>58119</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1305,27 +1305,27 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1334,10 +1334,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>637342</v>
+        <v>637340</v>
       </c>
       <c r="R8" t="n">
-        <v>7033896</v>
+        <v>7033940</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1399,7 +1399,7 @@
         <v>133733700</v>
       </c>
       <c r="B9" t="n">
-        <v>91885</v>
+        <v>91889</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1493,45 +1493,50 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133734358</v>
+        <v>133727622</v>
       </c>
       <c r="B10" t="n">
-        <v>97999</v>
+        <v>58444</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221945</v>
+        <v>103018</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Tjärdalsmyran, Tjärdalsmyran, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>637412</v>
+        <v>637334</v>
       </c>
       <c r="R10" t="n">
-        <v>7033897</v>
+        <v>7033909</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1590,50 +1595,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133727622</v>
+        <v>133734358</v>
       </c>
       <c r="B11" t="n">
-        <v>58444</v>
+        <v>98003</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103018</v>
+        <v>221945</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Tjärdalsmyran, Tjärdalsmyran, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>637334</v>
+        <v>637412</v>
       </c>
       <c r="R11" t="n">
-        <v>7033909</v>
+        <v>7033897</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -2083,7 +2083,7 @@
         <v>133734499</v>
       </c>
       <c r="B16" t="n">
-        <v>91885</v>
+        <v>91889</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2180,7 +2180,7 @@
         <v>133735008</v>
       </c>
       <c r="B17" t="n">
-        <v>91922</v>
+        <v>91926</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2274,10 +2274,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133728537</v>
+        <v>133730321</v>
       </c>
       <c r="B18" t="n">
-        <v>79334</v>
+        <v>91926</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2285,34 +2285,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Tjärdalsmyran, Tjärdalsmyran, Ång</t>
+          <t>Västra Hundberget, Västra Hundberget, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>637300</v>
+        <v>637161</v>
       </c>
       <c r="R18" t="n">
-        <v>7033916</v>
+        <v>7033917</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2371,10 +2371,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133730321</v>
+        <v>133728537</v>
       </c>
       <c r="B19" t="n">
-        <v>91922</v>
+        <v>79334</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2382,34 +2382,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Västra Hundberget, Västra Hundberget, Ång</t>
+          <t>Tjärdalsmyran, Tjärdalsmyran, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>637161</v>
+        <v>637300</v>
       </c>
       <c r="R19" t="n">
-        <v>7033917</v>
+        <v>7033916</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2471,7 +2471,7 @@
         <v>133730258</v>
       </c>
       <c r="B20" t="n">
-        <v>91885</v>
+        <v>91889</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2565,7 +2565,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133727574</v>
+        <v>133734225</v>
       </c>
       <c r="B21" t="n">
         <v>57958</v>
@@ -2605,10 +2605,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>637328</v>
+        <v>637416</v>
       </c>
       <c r="R21" t="n">
-        <v>7033886</v>
+        <v>7033933</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2645,7 +2645,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2672,7 +2672,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133734225</v>
+        <v>133727574</v>
       </c>
       <c r="B22" t="n">
         <v>57958</v>
@@ -2712,10 +2712,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>637416</v>
+        <v>637328</v>
       </c>
       <c r="R22" t="n">
-        <v>7033933</v>
+        <v>7033886</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2752,7 +2752,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Äldre ringhack, gran</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 21979-2026 artfynd.xlsx
+++ b/artfynd/A 21979-2026 artfynd.xlsx
@@ -1095,10 +1095,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133727592</v>
+        <v>133734508</v>
       </c>
       <c r="B6" t="n">
-        <v>57955</v>
+        <v>79334</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1106,39 +1106,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Tjärdalsmyran, Tjärdalsmyran, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>637342</v>
+        <v>637409</v>
       </c>
       <c r="R6" t="n">
-        <v>7033896</v>
+        <v>7033890</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1197,10 +1192,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133734508</v>
+        <v>133727592</v>
       </c>
       <c r="B7" t="n">
-        <v>79334</v>
+        <v>57955</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1208,34 +1203,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Tjärdalsmyran, Tjärdalsmyran, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>637409</v>
+        <v>637342</v>
       </c>
       <c r="R7" t="n">
-        <v>7033890</v>
+        <v>7033896</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1399,7 +1399,7 @@
         <v>133733700</v>
       </c>
       <c r="B9" t="n">
-        <v>91889</v>
+        <v>91891</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
         <v>133734358</v>
       </c>
       <c r="B11" t="n">
-        <v>98003</v>
+        <v>98005</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1886,7 +1886,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133734071</v>
+        <v>133729658</v>
       </c>
       <c r="B14" t="n">
         <v>79334</v>
@@ -1917,14 +1917,14 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Tjärdalsmyran, Tjärdalsmyran, Ång</t>
+          <t>Västra Hundberget, Västra Hundberget, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>637391</v>
+        <v>637114</v>
       </c>
       <c r="R14" t="n">
-        <v>7033944</v>
+        <v>7033888</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1983,7 +1983,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133729658</v>
+        <v>133734071</v>
       </c>
       <c r="B15" t="n">
         <v>79334</v>
@@ -2014,14 +2014,14 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Västra Hundberget, Västra Hundberget, Ång</t>
+          <t>Tjärdalsmyran, Tjärdalsmyran, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>637114</v>
+        <v>637391</v>
       </c>
       <c r="R15" t="n">
-        <v>7033888</v>
+        <v>7033944</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2083,7 +2083,7 @@
         <v>133734499</v>
       </c>
       <c r="B16" t="n">
-        <v>91889</v>
+        <v>91891</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2180,7 +2180,7 @@
         <v>133735008</v>
       </c>
       <c r="B17" t="n">
-        <v>91926</v>
+        <v>91928</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2277,7 +2277,7 @@
         <v>133730321</v>
       </c>
       <c r="B18" t="n">
-        <v>91926</v>
+        <v>91928</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         <v>133730258</v>
       </c>
       <c r="B20" t="n">
-        <v>91889</v>
+        <v>91891</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 21979-2026 artfynd.xlsx
+++ b/artfynd/A 21979-2026 artfynd.xlsx
@@ -1001,7 +1001,7 @@
         <v>133730284</v>
       </c>
       <c r="B5" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1095,10 +1095,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133734508</v>
+        <v>133727592</v>
       </c>
       <c r="B6" t="n">
-        <v>79334</v>
+        <v>57962</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1106,34 +1106,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Tjärdalsmyran, Tjärdalsmyran, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>637409</v>
+        <v>637342</v>
       </c>
       <c r="R6" t="n">
-        <v>7033890</v>
+        <v>7033896</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1192,10 +1197,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133727592</v>
+        <v>133733485</v>
       </c>
       <c r="B7" t="n">
-        <v>57955</v>
+        <v>58126</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1203,27 +1208,27 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1232,10 +1237,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>637342</v>
+        <v>637340</v>
       </c>
       <c r="R7" t="n">
-        <v>7033896</v>
+        <v>7033940</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1294,10 +1299,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133733485</v>
+        <v>133734508</v>
       </c>
       <c r="B8" t="n">
-        <v>58119</v>
+        <v>79348</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1305,39 +1310,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Tjärdalsmyran, Tjärdalsmyran, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>637340</v>
+        <v>637409</v>
       </c>
       <c r="R8" t="n">
-        <v>7033940</v>
+        <v>7033890</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1399,7 +1399,7 @@
         <v>133733700</v>
       </c>
       <c r="B9" t="n">
-        <v>91891</v>
+        <v>91910</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         <v>133727622</v>
       </c>
       <c r="B10" t="n">
-        <v>58444</v>
+        <v>58451</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
         <v>133734358</v>
       </c>
       <c r="B11" t="n">
-        <v>98005</v>
+        <v>98033</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1695,7 +1695,7 @@
         <v>133729318</v>
       </c>
       <c r="B12" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1792,7 +1792,7 @@
         <v>133733946</v>
       </c>
       <c r="B13" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>133729658</v>
       </c>
       <c r="B14" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
         <v>133734071</v>
       </c>
       <c r="B15" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2083,7 +2083,7 @@
         <v>133734499</v>
       </c>
       <c r="B16" t="n">
-        <v>91891</v>
+        <v>91910</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2180,7 +2180,7 @@
         <v>133735008</v>
       </c>
       <c r="B17" t="n">
-        <v>91928</v>
+        <v>91947</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2277,7 +2277,7 @@
         <v>133730321</v>
       </c>
       <c r="B18" t="n">
-        <v>91928</v>
+        <v>91947</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         <v>133728537</v>
       </c>
       <c r="B19" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         <v>133730258</v>
       </c>
       <c r="B20" t="n">
-        <v>91891</v>
+        <v>91910</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2565,10 +2565,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133734225</v>
+        <v>133727574</v>
       </c>
       <c r="B21" t="n">
-        <v>57958</v>
+        <v>57965</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2605,10 +2605,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>637416</v>
+        <v>637328</v>
       </c>
       <c r="R21" t="n">
-        <v>7033933</v>
+        <v>7033886</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2645,7 +2645,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Äldre ringhack, gran</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2672,10 +2672,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133727574</v>
+        <v>133734225</v>
       </c>
       <c r="B22" t="n">
-        <v>57958</v>
+        <v>57965</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2712,10 +2712,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>637328</v>
+        <v>637416</v>
       </c>
       <c r="R22" t="n">
-        <v>7033886</v>
+        <v>7033933</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2752,7 +2752,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 21979-2026 artfynd.xlsx
+++ b/artfynd/A 21979-2026 artfynd.xlsx
@@ -1095,10 +1095,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133727592</v>
+        <v>133734508</v>
       </c>
       <c r="B6" t="n">
-        <v>57962</v>
+        <v>79348</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1106,39 +1106,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Tjärdalsmyran, Tjärdalsmyran, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>637342</v>
+        <v>637409</v>
       </c>
       <c r="R6" t="n">
-        <v>7033896</v>
+        <v>7033890</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1299,10 +1294,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133734508</v>
+        <v>133727592</v>
       </c>
       <c r="B8" t="n">
-        <v>79348</v>
+        <v>57962</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1310,34 +1305,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Tjärdalsmyran, Tjärdalsmyran, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>637409</v>
+        <v>637342</v>
       </c>
       <c r="R8" t="n">
-        <v>7033890</v>
+        <v>7033896</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -2565,7 +2565,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133727574</v>
+        <v>133734225</v>
       </c>
       <c r="B21" t="n">
         <v>57965</v>
@@ -2605,10 +2605,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>637328</v>
+        <v>637416</v>
       </c>
       <c r="R21" t="n">
-        <v>7033886</v>
+        <v>7033933</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2645,7 +2645,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2672,7 +2672,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133734225</v>
+        <v>133727574</v>
       </c>
       <c r="B22" t="n">
         <v>57965</v>
@@ -2712,10 +2712,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>637416</v>
+        <v>637328</v>
       </c>
       <c r="R22" t="n">
-        <v>7033933</v>
+        <v>7033886</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2752,7 +2752,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Äldre ringhack, gran</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 21979-2026 artfynd.xlsx
+++ b/artfynd/A 21979-2026 artfynd.xlsx
@@ -1001,7 +1001,7 @@
         <v>133730284</v>
       </c>
       <c r="B5" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1095,10 +1095,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133734508</v>
+        <v>133733485</v>
       </c>
       <c r="B6" t="n">
-        <v>79348</v>
+        <v>58136</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1106,34 +1106,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Tjärdalsmyran, Tjärdalsmyran, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>637409</v>
+        <v>637340</v>
       </c>
       <c r="R6" t="n">
-        <v>7033890</v>
+        <v>7033940</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1192,10 +1197,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133733485</v>
+        <v>133734508</v>
       </c>
       <c r="B7" t="n">
-        <v>58126</v>
+        <v>79358</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1203,39 +1208,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Tjärdalsmyran, Tjärdalsmyran, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>637340</v>
+        <v>637409</v>
       </c>
       <c r="R7" t="n">
-        <v>7033940</v>
+        <v>7033890</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1297,7 +1297,7 @@
         <v>133727592</v>
       </c>
       <c r="B8" t="n">
-        <v>57962</v>
+        <v>57972</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
         <v>133733700</v>
       </c>
       <c r="B9" t="n">
-        <v>91910</v>
+        <v>91920</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         <v>133727622</v>
       </c>
       <c r="B10" t="n">
-        <v>58451</v>
+        <v>58461</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
         <v>133734358</v>
       </c>
       <c r="B11" t="n">
-        <v>98033</v>
+        <v>98043</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1695,7 +1695,7 @@
         <v>133729318</v>
       </c>
       <c r="B12" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1792,7 +1792,7 @@
         <v>133733946</v>
       </c>
       <c r="B13" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1886,10 +1886,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133729658</v>
+        <v>133734071</v>
       </c>
       <c r="B14" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1917,14 +1917,14 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Västra Hundberget, Västra Hundberget, Ång</t>
+          <t>Tjärdalsmyran, Tjärdalsmyran, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>637114</v>
+        <v>637391</v>
       </c>
       <c r="R14" t="n">
-        <v>7033888</v>
+        <v>7033944</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1983,10 +1983,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133734071</v>
+        <v>133729658</v>
       </c>
       <c r="B15" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2014,14 +2014,14 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Tjärdalsmyran, Tjärdalsmyran, Ång</t>
+          <t>Västra Hundberget, Västra Hundberget, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>637391</v>
+        <v>637114</v>
       </c>
       <c r="R15" t="n">
-        <v>7033944</v>
+        <v>7033888</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2083,7 +2083,7 @@
         <v>133734499</v>
       </c>
       <c r="B16" t="n">
-        <v>91910</v>
+        <v>91920</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2180,7 +2180,7 @@
         <v>133735008</v>
       </c>
       <c r="B17" t="n">
-        <v>91947</v>
+        <v>91957</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2274,10 +2274,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133730321</v>
+        <v>133728537</v>
       </c>
       <c r="B18" t="n">
-        <v>91947</v>
+        <v>79358</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2285,34 +2285,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Västra Hundberget, Västra Hundberget, Ång</t>
+          <t>Tjärdalsmyran, Tjärdalsmyran, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>637161</v>
+        <v>637300</v>
       </c>
       <c r="R18" t="n">
-        <v>7033917</v>
+        <v>7033916</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2371,45 +2371,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133728537</v>
+        <v>133730258</v>
       </c>
       <c r="B19" t="n">
-        <v>79348</v>
+        <v>91920</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Tjärdalsmyran, Tjärdalsmyran, Ång</t>
+          <t>Västra Hundberget, Västra Hundberget, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>637300</v>
+        <v>637117</v>
       </c>
       <c r="R19" t="n">
-        <v>7033916</v>
+        <v>7033918</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2468,32 +2468,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133730258</v>
+        <v>133730321</v>
       </c>
       <c r="B20" t="n">
-        <v>91910</v>
+        <v>91957</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2503,10 +2503,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>637117</v>
+        <v>637161</v>
       </c>
       <c r="R20" t="n">
-        <v>7033918</v>
+        <v>7033917</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2568,7 +2568,7 @@
         <v>133734225</v>
       </c>
       <c r="B21" t="n">
-        <v>57965</v>
+        <v>57975</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2675,7 +2675,7 @@
         <v>133727574</v>
       </c>
       <c r="B22" t="n">
-        <v>57965</v>
+        <v>57975</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 21979-2026 artfynd.xlsx
+++ b/artfynd/A 21979-2026 artfynd.xlsx
@@ -1095,10 +1095,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133733485</v>
+        <v>133734508</v>
       </c>
       <c r="B6" t="n">
-        <v>58136</v>
+        <v>79358</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1106,39 +1106,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Tjärdalsmyran, Tjärdalsmyran, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>637340</v>
+        <v>637409</v>
       </c>
       <c r="R6" t="n">
-        <v>7033940</v>
+        <v>7033890</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1197,10 +1192,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133734508</v>
+        <v>133733485</v>
       </c>
       <c r="B7" t="n">
-        <v>79358</v>
+        <v>58136</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1208,34 +1203,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Tjärdalsmyran, Tjärdalsmyran, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>637409</v>
+        <v>637340</v>
       </c>
       <c r="R7" t="n">
-        <v>7033890</v>
+        <v>7033940</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1886,7 +1886,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133734071</v>
+        <v>133729658</v>
       </c>
       <c r="B14" t="n">
         <v>79358</v>
@@ -1917,14 +1917,14 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Tjärdalsmyran, Tjärdalsmyran, Ång</t>
+          <t>Västra Hundberget, Västra Hundberget, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>637391</v>
+        <v>637114</v>
       </c>
       <c r="R14" t="n">
-        <v>7033944</v>
+        <v>7033888</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1983,7 +1983,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133729658</v>
+        <v>133734071</v>
       </c>
       <c r="B15" t="n">
         <v>79358</v>
@@ -2014,14 +2014,14 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Västra Hundberget, Västra Hundberget, Ång</t>
+          <t>Tjärdalsmyran, Tjärdalsmyran, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>637114</v>
+        <v>637391</v>
       </c>
       <c r="R15" t="n">
-        <v>7033888</v>
+        <v>7033944</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2274,10 +2274,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133728537</v>
+        <v>133730321</v>
       </c>
       <c r="B18" t="n">
-        <v>79358</v>
+        <v>91957</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2285,34 +2285,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Tjärdalsmyran, Tjärdalsmyran, Ång</t>
+          <t>Västra Hundberget, Västra Hundberget, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>637300</v>
+        <v>637161</v>
       </c>
       <c r="R18" t="n">
-        <v>7033916</v>
+        <v>7033917</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2468,10 +2468,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133730321</v>
+        <v>133728537</v>
       </c>
       <c r="B20" t="n">
-        <v>91957</v>
+        <v>79358</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2479,34 +2479,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Västra Hundberget, Västra Hundberget, Ång</t>
+          <t>Tjärdalsmyran, Tjärdalsmyran, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>637161</v>
+        <v>637300</v>
       </c>
       <c r="R20" t="n">
-        <v>7033917</v>
+        <v>7033916</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>

--- a/artfynd/A 21979-2026 artfynd.xlsx
+++ b/artfynd/A 21979-2026 artfynd.xlsx
@@ -1095,10 +1095,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133734508</v>
+        <v>133733485</v>
       </c>
       <c r="B6" t="n">
-        <v>79358</v>
+        <v>58136</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1106,34 +1106,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Tjärdalsmyran, Tjärdalsmyran, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>637409</v>
+        <v>637340</v>
       </c>
       <c r="R6" t="n">
-        <v>7033890</v>
+        <v>7033940</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1192,10 +1197,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133733485</v>
+        <v>133727592</v>
       </c>
       <c r="B7" t="n">
-        <v>58136</v>
+        <v>57972</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1203,27 +1208,27 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1232,10 +1237,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>637340</v>
+        <v>637342</v>
       </c>
       <c r="R7" t="n">
-        <v>7033940</v>
+        <v>7033896</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1294,10 +1299,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133727592</v>
+        <v>133734508</v>
       </c>
       <c r="B8" t="n">
-        <v>57972</v>
+        <v>79358</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1305,39 +1310,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Tjärdalsmyran, Tjärdalsmyran, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>637342</v>
+        <v>637409</v>
       </c>
       <c r="R8" t="n">
-        <v>7033896</v>
+        <v>7033890</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -2371,45 +2371,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133730258</v>
+        <v>133728537</v>
       </c>
       <c r="B19" t="n">
-        <v>91920</v>
+        <v>79358</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Västra Hundberget, Västra Hundberget, Ång</t>
+          <t>Tjärdalsmyran, Tjärdalsmyran, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>637117</v>
+        <v>637300</v>
       </c>
       <c r="R19" t="n">
-        <v>7033918</v>
+        <v>7033916</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2468,45 +2468,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133728537</v>
+        <v>133730258</v>
       </c>
       <c r="B20" t="n">
-        <v>79358</v>
+        <v>91920</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Tjärdalsmyran, Tjärdalsmyran, Ång</t>
+          <t>Västra Hundberget, Västra Hundberget, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>637300</v>
+        <v>637117</v>
       </c>
       <c r="R20" t="n">
-        <v>7033916</v>
+        <v>7033918</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>

--- a/artfynd/A 21979-2026 artfynd.xlsx
+++ b/artfynd/A 21979-2026 artfynd.xlsx
@@ -1001,7 +1001,7 @@
         <v>133730284</v>
       </c>
       <c r="B5" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1197,10 +1197,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133727592</v>
+        <v>133734508</v>
       </c>
       <c r="B7" t="n">
-        <v>57972</v>
+        <v>79359</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1208,39 +1208,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Tjärdalsmyran, Tjärdalsmyran, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>637342</v>
+        <v>637409</v>
       </c>
       <c r="R7" t="n">
-        <v>7033896</v>
+        <v>7033890</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1299,10 +1294,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133734508</v>
+        <v>133727592</v>
       </c>
       <c r="B8" t="n">
-        <v>79358</v>
+        <v>57972</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1310,34 +1305,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Tjärdalsmyran, Tjärdalsmyran, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>637409</v>
+        <v>637342</v>
       </c>
       <c r="R8" t="n">
-        <v>7033890</v>
+        <v>7033896</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1399,7 +1399,7 @@
         <v>133733700</v>
       </c>
       <c r="B9" t="n">
-        <v>91920</v>
+        <v>91922</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
         <v>133734358</v>
       </c>
       <c r="B11" t="n">
-        <v>98043</v>
+        <v>98045</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1695,7 +1695,7 @@
         <v>133729318</v>
       </c>
       <c r="B12" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1792,7 +1792,7 @@
         <v>133733946</v>
       </c>
       <c r="B13" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1886,10 +1886,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133729658</v>
+        <v>133734071</v>
       </c>
       <c r="B14" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1917,14 +1917,14 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Västra Hundberget, Västra Hundberget, Ång</t>
+          <t>Tjärdalsmyran, Tjärdalsmyran, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>637114</v>
+        <v>637391</v>
       </c>
       <c r="R14" t="n">
-        <v>7033888</v>
+        <v>7033944</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1983,10 +1983,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133734071</v>
+        <v>133729658</v>
       </c>
       <c r="B15" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2014,14 +2014,14 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Tjärdalsmyran, Tjärdalsmyran, Ång</t>
+          <t>Västra Hundberget, Västra Hundberget, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>637391</v>
+        <v>637114</v>
       </c>
       <c r="R15" t="n">
-        <v>7033944</v>
+        <v>7033888</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2083,7 +2083,7 @@
         <v>133734499</v>
       </c>
       <c r="B16" t="n">
-        <v>91920</v>
+        <v>91922</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2180,7 +2180,7 @@
         <v>133735008</v>
       </c>
       <c r="B17" t="n">
-        <v>91957</v>
+        <v>91959</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2277,7 +2277,7 @@
         <v>133730321</v>
       </c>
       <c r="B18" t="n">
-        <v>91957</v>
+        <v>91959</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         <v>133728537</v>
       </c>
       <c r="B19" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         <v>133730258</v>
       </c>
       <c r="B20" t="n">
-        <v>91920</v>
+        <v>91922</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 21979-2026 artfynd.xlsx
+++ b/artfynd/A 21979-2026 artfynd.xlsx
@@ -1197,10 +1197,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133734508</v>
+        <v>133727592</v>
       </c>
       <c r="B7" t="n">
-        <v>79359</v>
+        <v>57972</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1208,34 +1208,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Tjärdalsmyran, Tjärdalsmyran, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>637409</v>
+        <v>637342</v>
       </c>
       <c r="R7" t="n">
-        <v>7033890</v>
+        <v>7033896</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1294,10 +1299,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133727592</v>
+        <v>133734508</v>
       </c>
       <c r="B8" t="n">
-        <v>57972</v>
+        <v>79359</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1305,39 +1310,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Tjärdalsmyran, Tjärdalsmyran, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>637342</v>
+        <v>637409</v>
       </c>
       <c r="R8" t="n">
-        <v>7033896</v>
+        <v>7033890</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>

--- a/artfynd/A 21979-2026 artfynd.xlsx
+++ b/artfynd/A 21979-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY29"/>
+  <dimension ref="A1:AZ29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133728865</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133729510</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -967,6 +982,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113712722</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1068,6 +1088,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113712723</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1165,6 +1190,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133730321</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1262,6 +1292,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133735008</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1359,6 +1394,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133727459</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1456,6 +1496,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133728738</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1553,6 +1598,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133730258</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1650,6 +1700,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133733700</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1747,6 +1802,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133734499</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1853,6 +1913,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113712724</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1950,6 +2015,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133727358</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2047,6 +2117,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133728537</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2144,6 +2219,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133729318</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2241,6 +2321,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133729658</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2338,6 +2423,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133729721</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2435,6 +2525,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133730284</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2532,6 +2627,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133733946</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2629,6 +2729,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133734071</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2726,6 +2831,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133734508</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2828,6 +2938,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133727592</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2935,6 +3050,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133727574</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3042,6 +3162,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133734225</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3148,6 +3273,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113712721</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3250,6 +3380,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133727622</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3352,6 +3487,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133733485</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3449,8 +3589,43 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133734358</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>